--- a/date.xlsx
+++ b/date.xlsx
@@ -55,7 +55,7 @@
     <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=150%&gt;不想早起口牙&lt;/size&gt;</t>
   </si>
   <si>
-    <t>&lt;b&gt;上计组&lt;/b&gt;</t>
+    <t>&lt;b&gt;上计组第1节&lt;/b&gt;</t>
   </si>
   <si>
     <t>与蒂娜玩</t>
@@ -67,97 +67,97 @@
     <t>05_17</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=151%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第2节&lt;/b&gt;</t>
   </si>
   <si>
     <t>05_18</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=152%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第3节&lt;/b&gt;</t>
   </si>
   <si>
     <t>05_19</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=153%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第4节&lt;/b&gt;</t>
   </si>
   <si>
     <t>05_20</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=154%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第5节&lt;/b&gt;</t>
   </si>
   <si>
     <t>05_21</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=155%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第6节&lt;/b&gt;</t>
   </si>
   <si>
     <t>05_22</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=156%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第7节&lt;/b&gt;</t>
   </si>
   <si>
     <t>05_23</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=157%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第8节&lt;/b&gt;</t>
   </si>
   <si>
     <t>05_24</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=158%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第9节&lt;/b&gt;</t>
   </si>
   <si>
     <t>05_25</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=159%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第10节&lt;/b&gt;</t>
   </si>
   <si>
     <t>05_26</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=160%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第11节&lt;/b&gt;</t>
   </si>
   <si>
     <t>05_27</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=161%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第12节&lt;/b&gt;</t>
   </si>
   <si>
     <t>05_28</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=162%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第13节&lt;/b&gt;</t>
   </si>
   <si>
     <t>05_29</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=163%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第14节&lt;/b&gt;</t>
   </si>
   <si>
     <t>05_30</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=164%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第15节&lt;/b&gt;</t>
   </si>
   <si>
     <t>05_31</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=165%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第16节&lt;/b&gt;</t>
   </si>
   <si>
     <t>06_01</t>
   </si>
   <si>
-    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=166%&gt;不想早起口牙&lt;/size&gt;</t>
+    <t>&lt;b&gt;上计组第17节&lt;/b&gt;</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="42" spans="1:6">
+    <row r="2" ht="28" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="42" spans="1:6">
+    <row r="3" ht="28" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1148,11 +1148,11 @@
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="42" spans="1:6">
+    <row r="4" ht="28" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1168,11 +1168,11 @@
         <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="42" spans="1:6">
+    <row r="5" ht="28" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1188,11 +1188,11 @@
         <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="42" spans="1:6">
+    <row r="6" ht="28" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1208,11 +1208,11 @@
         <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="42" spans="1:6">
+    <row r="7" ht="28" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1228,11 +1228,11 @@
         <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" ht="42" spans="1:6">
+    <row r="8" ht="28" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1248,11 +1248,11 @@
         <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="42" spans="1:6">
+    <row r="9" ht="28" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1268,11 +1268,11 @@
         <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" ht="42" spans="1:6">
+    <row r="10" ht="28" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1288,11 +1288,11 @@
         <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" ht="42" spans="1:6">
+    <row r="11" ht="28" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1308,11 +1308,11 @@
         <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E11" s="1" t="s">
         <v>9</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="42" spans="1:6">
+    <row r="12" ht="28" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1328,11 +1328,11 @@
         <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E12" s="1" t="s">
         <v>9</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="42" spans="1:6">
+    <row r="13" ht="28" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1348,11 +1348,11 @@
         <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" ht="42" spans="1:6">
+    <row r="14" ht="28" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1368,11 +1368,11 @@
         <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" ht="42" spans="1:6">
+    <row r="15" ht="28" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1388,11 +1388,11 @@
         <v>35</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E15" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" ht="42" spans="1:6">
+    <row r="16" ht="28" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1408,11 +1408,11 @@
         <v>37</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E16" s="1" t="s">
         <v>9</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" ht="42" spans="1:6">
+    <row r="17" ht="28" spans="1:6">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1428,11 +1428,11 @@
         <v>39</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E17" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,7 +1440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" ht="42" spans="1:6">
+    <row r="18" ht="28" spans="1:6">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1448,10 +1448,10 @@
         <v>41</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>9</v>

--- a/date.xlsx
+++ b/date.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="42">
   <si>
     <t>day</t>
   </si>
@@ -49,7 +49,7 @@
     <t>text</t>
   </si>
   <si>
-    <t>05_16</t>
+    <t>09_01</t>
   </si>
   <si>
     <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=150%&gt;不想早起口牙&lt;/size&gt;</t>
@@ -64,97 +64,94 @@
     <t>今天蒂娜似乎心情很好</t>
   </si>
   <si>
-    <t>05_17</t>
+    <t>09_02</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第2节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>05_18</t>
+    <t>09_03</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第3节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>05_19</t>
+    <t>09_04</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第4节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>05_20</t>
+    <t>09_07</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第5节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>05_21</t>
+    <t>09_06</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第6节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>05_22</t>
-  </si>
-  <si>
     <t>&lt;b&gt;上计组第7节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>05_23</t>
+    <t>09_08</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第8节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>05_24</t>
+    <t>09_09</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第9节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>05_25</t>
+    <t>09_10</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第10节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>05_26</t>
+    <t>09_11</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第11节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>05_27</t>
+    <t>09_14</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第12节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>05_28</t>
+    <t>09_15</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第13节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>05_29</t>
+    <t>09_16</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第14节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>05_30</t>
+    <t>09_17</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第15节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>05_31</t>
+    <t>09_18</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第16节&lt;/b&gt;</t>
   </si>
   <si>
-    <t>06_01</t>
+    <t>09_19</t>
   </si>
   <si>
     <t>&lt;b&gt;上计组第17节&lt;/b&gt;</t>
@@ -323,12 +320,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -649,7 +652,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -673,16 +676,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -691,94 +694,97 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1184,7 +1190,7 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1245,13 +1251,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>9</v>
@@ -1265,13 +1271,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>9</v>
@@ -1285,13 +1291,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>9</v>
@@ -1305,13 +1311,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>9</v>
@@ -1324,14 +1330,14 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>9</v>
@@ -1345,13 +1351,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>9</v>
@@ -1365,13 +1371,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>9</v>
@@ -1385,13 +1391,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>9</v>
@@ -1405,13 +1411,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>9</v>
@@ -1425,13 +1431,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>9</v>
@@ -1445,13 +1451,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>9</v>

--- a/date.xlsx
+++ b/date.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="43">
   <si>
     <t>day</t>
   </si>
@@ -52,73 +52,76 @@
     <t>09_01</t>
   </si>
   <si>
+    <t xml:space="preserve">&lt;b&gt;开学仪式&lt;/b&gt;\n </t>
+  </si>
+  <si>
+    <t>&lt;b&gt;上课&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>与蒂娜玩</t>
+  </si>
+  <si>
+    <t>今天认识了一个奇怪的人</t>
+  </si>
+  <si>
+    <t>09_02</t>
+  </si>
+  <si>
     <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=150%&gt;不想早起口牙&lt;/size&gt;</t>
   </si>
   <si>
-    <t>&lt;b&gt;上计组第1节&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>与蒂娜玩</t>
-  </si>
-  <si>
     <t>今天蒂娜似乎心情很好</t>
   </si>
   <si>
-    <t>09_02</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;上计组第2节&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>09_03</t>
   </si>
   <si>
-    <t>&lt;b&gt;上计组第3节&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>09_04</t>
   </si>
   <si>
-    <t>&lt;b&gt;上计组第4节&lt;/b&gt;</t>
+    <t>今天似乎是很关键的日子</t>
+  </si>
+  <si>
+    <t>09_05</t>
+  </si>
+  <si>
+    <t>周末，可以自由安排</t>
+  </si>
+  <si>
+    <t>09_06</t>
+  </si>
+  <si>
+    <t>去打乒乓球</t>
+  </si>
+  <si>
+    <t>周末，应该会去打乒乓球</t>
   </si>
   <si>
     <t>09_07</t>
   </si>
   <si>
-    <t>&lt;b&gt;上计组第5节&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>09_06</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;上计组第6节&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;上计组第7节&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>09_08</t>
   </si>
   <si>
-    <t>&lt;b&gt;上计组第8节&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>09_09</t>
   </si>
   <si>
-    <t>&lt;b&gt;上计组第9节&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>09_10</t>
   </si>
   <si>
-    <t>&lt;b&gt;上计组第10节&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>09_11</t>
   </si>
   <si>
-    <t>&lt;b&gt;上计组第11节&lt;/b&gt;</t>
+    <t>09_12</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;上早八&lt;/b&gt;\n &lt;size=151%&gt;不想早起口牙&lt;/size&gt;</t>
+  </si>
+  <si>
+    <t>周末，但似乎有不祥的预感</t>
+  </si>
+  <si>
+    <t>09_13</t>
   </si>
   <si>
     <t>09_14</t>
@@ -320,7 +323,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -330,6 +333,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,7 +661,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -676,16 +685,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -694,89 +703,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -784,6 +793,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1097,7 +1109,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="28.3636363636364" style="1" customWidth="1"/>
@@ -1154,16 +1166,16 @@
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:6">
@@ -1171,19 +1183,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:6">
@@ -1194,276 +1206,326 @@
         <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" ht="28" spans="1:6">
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:6">
       <c r="A8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" ht="28" spans="1:6">
       <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="E9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" ht="28" spans="1:6">
       <c r="A10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" ht="28" spans="1:6">
       <c r="A11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" ht="28" spans="1:6">
       <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" ht="28" spans="1:6">
       <c r="A13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" ht="28" spans="1:6">
       <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="15" ht="28" spans="1:6">
       <c r="A15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" ht="28" spans="1:6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="28" spans="1:6">
       <c r="A17">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" ht="28" spans="1:6">
       <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" ht="28" spans="1:6">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" ht="28" spans="1:6">
+      <c r="A20">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" ht="28" spans="1:6">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="E21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" ht="28" spans="1:6">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>10</v>
+      <c r="C22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
